--- a/ut_pid_model_inputs - Viridian Farm.xlsx
+++ b/ut_pid_model_inputs - Viridian Farm.xlsx
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,9 +173,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -546,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:K99"/>
+  <dimension ref="B1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -618,7 +615,7 @@
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Metro District Name</t>
+          <t>Public Infrastructure District Name</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1620,7 +1617,7 @@
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Strict Biennial Level-of-Value</t>
+          <t>Hold Value Flat Between Reassessments</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -1630,7 +1627,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>STRICT_BIENNIAL_AV</t>
+          <t>HOLD_VALUE_FLAT</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -1755,7 +1752,11 @@
           <t>REASSESS_RATE</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>applied annually in Utah</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
@@ -1787,7 +1788,11 @@
           <t>RESID_TAXABLE_RATIO</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>55% — the 45% exemption, § 59-2-103</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
@@ -1805,7 +1810,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>residential taxable ratio when the governing document was adopted</t>
+          <t>ratio before the current exemption</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2002,7 @@
     <row r="83">
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Lot / Home Valuation</t>
+          <t>Lot / Home Ratios</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2020,23 @@
           <t>LOT_INVENTORY_TAXABLE_RATIO</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr"/>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>55% under Utah Admin. Code R884-24P-52; 100% to tax at full market</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>Platted Lot Value (% of ASP)</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>PLATTED_LOT_VALUE</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>lot value = ASP × this (default 10%)</t>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Lot / Home Valuation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Platted Commercial Lot Value</t>
+          <t>Platted Lot Value (% of ASP)</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
@@ -2048,42 +2044,42 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
+          <t>PLATTED_LOT_VALUE</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>lot value = ASP × this (default 10%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Platted Commercial Lot Value</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
           <t>PLATTED_COMM_LOT_VALUE</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="B87" s="4" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>Centrally Assessed / Commercial</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Centrally Assessed Property (market value)</t>
-        </is>
-      </c>
-      <c r="C88" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>CENTRALLY_ASSESSED_VALUE</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t>$ actual</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Centrally Assessed Equipment (market value)</t>
+          <t>Centrally Assessed Property (market value)</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
@@ -2091,85 +2087,89 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>CENTRALLY_ASSESSED_EQUIPMENT</t>
+          <t>CENTRALLY_ASSESSED_VALUE</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>$ actual</t>
+          <t>$ market — § 59-2-201</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Centrally Assessed Taxable Ratio</t>
-        </is>
-      </c>
-      <c r="C90" s="12" t="n">
-        <v>0.875</v>
+          <t>Centrally Assessed Equipment (market value)</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>CENTRALLY_ASSESSED_RATIO</t>
+          <t>CENTRALLY_ASSESSED_EQUIPMENT</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>market value × ratio</t>
+          <t>$ market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Include Centrally Assessed in Taxed Value</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>Centrally Assessed Taxable Ratio</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="n">
+        <v>0.875</v>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>CENTRALLY_ASSESSED</t>
+          <t>CENTRALLY_ASSESSED_RATIO</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>market value × ratio</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Commercial Taxable Ratio</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="n">
-        <v>0.29</v>
+          <t>Include Centrally Assessed in Taxed Value</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>COMMERCIAL_ASSESSMENT_RATIO</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr"/>
+          <t>CENTRALLY_ASSESSED</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Commercial AV Lag (years)</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="n">
-        <v>2</v>
+          <t>Commercial Taxable Ratio</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="n">
+        <v>0.29</v>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>COMM_ASSESSMENT_LAG_YEARS</t>
+          <t>COMMERCIAL_ASSESSMENT_RATIO</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr"/>
@@ -2177,133 +2177,150 @@
     <row r="94">
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Include Commercial in Taxed Value</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
+          <t>Commercial AV Lag (years)</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>COMM_ASSESSMENT_LAG_YEARS</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Include Commercial in Taxed AV</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>COMM_NEW_VALUE_ADD</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>Yes/No</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="4" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>District Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>Annual District Administration</t>
-        </is>
-      </c>
-      <c r="C96" s="10" t="n">
-        <v>53060</v>
-      </c>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>ADMIN_COST</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>$ per year, charged against pledged revenue</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>District Administration Growth Rate</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="n">
-        <v>0.02</v>
+          <t>Annual District Administration</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="n">
+        <v>53060</v>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>ADMIN_GROWTH_RATE</t>
+          <t>ADMIN_COST</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>annual inflation on the administration base</t>
+          <t>$ per year, charged against pledged revenue</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>District Administration Taxable Value Limit</t>
-        </is>
-      </c>
-      <c r="C98" s="10" t="n">
-        <v>0</v>
+          <t>District Administration Growth Rate</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>0.02</v>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>ADMIN_COST_AV_LIMIT</t>
+          <t>ADMIN_GROWTH_RATE</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>$ — above this taxable value the charge stops; 0 ⇒ no limit</t>
+          <t>annual inflation on the administration base</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
+          <t>District Administration Taxable Value Limit</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>ADMIN_COST_AV_LIMIT</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>$ — above this taxable value the charge stops; 0 ⇒ no limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="6" t="inlineStr">
+        <is>
           <t>First Year District Costs Are Charged</t>
         </is>
       </c>
-      <c r="C99" s="7" t="n"/>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="C100" s="7" t="n"/>
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>DISTRICT_COST_START_YEAR</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>blank ⇒ two years after closing</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B56:E56"/>
+  <mergeCells count="19">
     <mergeCell ref="B83:E83"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B62:E62"/>
     <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B87:E87"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="G5:K5"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B95:E95"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B34:E34"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C19 C20 C21 C22 C23 C91 C94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C19 C20 C21 C22 C23 C92 C95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="C61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -4054,7 +4071,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Reference only. Utah taxes primary residential property on 55% of fair market value — the 45% exemption of Utah Const. art. XIII, § 3 and Utah Code § 59-2-103, covering the dwelling and up to one acre of land. Informs RESID_TAXABLE_RATIO and RESID_TAXABLE_RATIO_PRIOR on the Inputs tab.</t>
+          <t>EDITABLE — Utah taxes primary residential property on 55% of fair market value — the 45% exemption of Utah Const. art. XIII, § 3 and Utah Code § 59-2-103, covering the dwelling and up to one acre of land. The rate has been flat at 55% since 1995. The model READS these yellow cells and applies them to residential value by roll year (carry-forward past the last row); the RESID_TAXABLE_RATIO cell on the Inputs tab overrides them when changed.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4098,7 @@
           <t>1982–1984</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="12" t="n">
         <v>0.75</v>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -4096,7 +4113,7 @@
           <t>1985–1994</t>
         </is>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="12" t="n">
         <v>0.68</v>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -4111,7 +4128,7 @@
           <t>1995 +</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="12" t="n">
         <v>0.55</v>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -4123,7 +4140,7 @@
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Colorado Vacant-Land / Nonresidential Taxable Ratios</t>
+          <t>Utah Builder Lot Inventory Taxable Ratios</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4330,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>

--- a/ut_pid_model_inputs - Viridian Farm.xlsx
+++ b/ut_pid_model_inputs - Viridian Farm.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:K100"/>
+  <dimension ref="B1:K102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2282,16 +2282,56 @@
     <row r="100">
       <c r="B100" s="6" t="inlineStr">
         <is>
+          <t>Starting O&amp;M Expense</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>OM_EXPENSE</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>$ per year of district operations &amp; maintenance, netted from the revenue available to both liens</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>O&amp;M Expense Growth Rate</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>OM_GROWTH_RATE</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>annual inflation on the O&amp;M base</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="6" t="inlineStr">
+        <is>
           <t>First Year District Costs Are Charged</t>
         </is>
       </c>
-      <c r="C100" s="7" t="n"/>
-      <c r="D100" s="8" t="inlineStr">
+      <c r="C102" s="7" t="n"/>
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>DISTRICT_COST_START_YEAR</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>blank ⇒ two years after closing</t>
         </is>

--- a/ut_pid_model_inputs - Viridian Farm.xlsx
+++ b/ut_pid_model_inputs - Viridian Farm.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:K102"/>
+  <dimension ref="B1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1689,51 +1689,55 @@
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Inflation Start Year</t>
+          <t>Projection Horizon (years from delivery)</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>2025</v>
+        <v>40</v>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>INFLATION_START_YEAR</t>
+          <t>PROJECTION_YEARS</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>home-price inflation begins this year; flat (not deflated) before</t>
+          <t>development, AV, revenue &amp; summary tabs run this many years</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Inflation Rate (home prices)</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="n">
-        <v>0.03</v>
+          <t>Inflation Start Year</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>2025</v>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>INFLATION_RATE</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr"/>
+          <t>INFLATION_START_YEAR</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>home-price inflation begins this year; flat (not deflated) before</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Inflation Rate (commercial sales)</t>
+          <t>Inflation Rate (home prices)</t>
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>INFLATION_RATE_COMM_SALES</t>
+          <t>INFLATION_RATE</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr"/>
@@ -1741,7 +1745,7 @@
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Reassessment - Residential</t>
+          <t>Inflation Rate (commercial sales)</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
@@ -1749,622 +1753,699 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>REASSESS_RATE</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>applied annually in Utah</t>
-        </is>
-      </c>
+          <t>INFLATION_RATE_COMM_SALES</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Reassessment - Commercial</t>
+          <t>Reassessment - Residential</t>
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>REASSESS_COMM_RATE</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr"/>
+          <t>REASSESS_RATE</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>applied annually in Utah</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Primary Residential Taxable Ratio</t>
+          <t>Reassessment - Commercial</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>0.55</v>
+        <v>0.02</v>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>RESID_TAXABLE_RATIO</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>55% — the 45% exemption, § 59-2-103</t>
-        </is>
-      </c>
+          <t>REASSESS_COMM_RATE</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>Prior Residential Taxable Ratio</t>
-        </is>
-      </c>
-      <c r="C72" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>RESID_TAXABLE_RATIO_PRIOR</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>ratio before the current exemption</t>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Developer Contribution</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Mill Levy Tax Collection %</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="n">
-        <v>0.98</v>
+          <t>Developer Contribution ($)</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>TAX_COLLECT_MILL_PRC</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr"/>
+          <t>DEVELOPER_CONTRIBUTION</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>cash contributed by the developer (a source of funds)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Personal Property Uniform Fee %</t>
-        </is>
-      </c>
-      <c r="C74" s="12" t="n">
-        <v>0</v>
+          <t>Applied To (Senior / Subordinate / Proportional)</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Proportional</t>
+        </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>UNIFORM_FEE_PRC</t>
+          <t>DEVELOPER_CONTRIBUTION_SERIES</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>§ 59-2-405; % of mill revenue</t>
+          <t>which series the contribution funds; Proportional spreads it by par</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Uniform Fee Taxable Value Threshold</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>UNIFORM_FEE_AV_THRESHOLD</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>$</t>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Tax &amp; Valuation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Reassessment Frequency</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
+          <t>Primary Residential Taxable Ratio</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="n">
+        <v>0.55</v>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>REASSESS_FREQUENCY</t>
+          <t>RESID_TAXABLE_RATIO</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Annual (Utah, § 59-2-303.1) or Biennial (Colorado cadence)</t>
+          <t>55% — the 45% exemption, § 59-2-103</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Mill Levies</t>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Prior Residential Taxable Ratio</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>RESID_TAXABLE_RATIO_PRIOR</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>ratio before the current exemption</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Mill Levy — Governing Document Cap</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="n">
-        <v>5</v>
+          <t>Mill Levy Tax Collection %</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="n">
+        <v>0.98</v>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>MILL_LEVY_GOVERNING_DOC</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>mills</t>
-        </is>
-      </c>
+          <t>TAX_COLLECT_MILL_PRC</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Mill Levy — Indenture Cap</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="n">
-        <v>3</v>
+          <t>Personal Property Uniform Fee %</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>MILL_LEVY_INDENTURE</t>
+          <t>UNIFORM_FEE_PRC</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>mills; blank ⇒ no indenture cap</t>
+          <t>§ 59-2-405; % of mill revenue</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Mill Levy Target - Debt Service</t>
+          <t>Uniform Fee Taxable Value Threshold</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>MILL_LEVY_DS_TARGET</t>
+          <t>UNIFORM_FEE_AV_THRESHOLD</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>mills</t>
+          <t>$</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Mill Levy - Commercial</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="n">
-        <v>3</v>
+          <t>Reassessment Frequency</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>MILL_LEVY_COMM</t>
+          <t>REASSESS_FREQUENCY</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
+          <t>Annual (Utah, § 59-2-303.1) or Biennial (Colorado cadence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Mill Levies</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Mill Levy — Governing Document Cap</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>MILL_LEVY_GOVERNING_DOC</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
           <t>mills</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>Mill Levy Target - Operations</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>MILL_LEVY_OPS_TARGET</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>mills</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Lot / Home Ratios</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Builder Lot Inventory Taxable Ratio</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="n">
-        <v>0.55</v>
+          <t>Mill Levy — Indenture Cap</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>LOT_INVENTORY_TAXABLE_RATIO</t>
+          <t>MILL_LEVY_INDENTURE</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>55% under Utah Admin. Code R884-24P-52; 100% to tax at full market</t>
+          <t>mills; blank ⇒ no indenture cap</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Lot / Home Valuation</t>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Mill Levy Target - Debt Service</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>MILL_LEVY_DS_TARGET</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>mills</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Platted Lot Value (% of ASP)</t>
-        </is>
-      </c>
-      <c r="C86" s="12" t="n">
-        <v>0.1</v>
+          <t>Mill Levy - Commercial</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>PLATTED_LOT_VALUE</t>
+          <t>MILL_LEVY_COMM</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>lot value = ASP × this (default 10%)</t>
+          <t>mills</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Platted Commercial Lot Value</t>
-        </is>
-      </c>
-      <c r="C87" s="12" t="n">
-        <v>0.1</v>
+          <t>Mill Levy Target - Operations</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>PLATTED_COMM_LOT_VALUE</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr"/>
+          <t>MILL_LEVY_OPS_TARGET</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>mills</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Centrally Assessed / Commercial</t>
+          <t>Lot / Home Ratios</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Centrally Assessed Property (market value)</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="n">
-        <v>0</v>
+          <t>Builder Lot Inventory Taxable Ratio</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="n">
+        <v>0.55</v>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>CENTRALLY_ASSESSED_VALUE</t>
+          <t>LOT_INVENTORY_TAXABLE_RATIO</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>$ market — § 59-2-201</t>
+          <t>55% under Utah Admin. Code R884-24P-52; 100% to tax at full market</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>Centrally Assessed Equipment (market value)</t>
-        </is>
-      </c>
-      <c r="C90" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>CENTRALLY_ASSESSED_EQUIPMENT</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>$ market</t>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Lot / Home Valuation</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Centrally Assessed Taxable Ratio</t>
+          <t>Platted Lot Value (% of ASP)</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>0.875</v>
+        <v>0.1</v>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>CENTRALLY_ASSESSED_RATIO</t>
+          <t>PLATTED_LOT_VALUE</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>market value × ratio</t>
+          <t>lot value = ASP × this (default 10%)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Include Centrally Assessed in Taxed Value</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>Platted Commercial Lot Value</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="n">
+        <v>0.1</v>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>CENTRALLY_ASSESSED</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>Yes/No</t>
-        </is>
-      </c>
+          <t>PLATTED_COMM_LOT_VALUE</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Commercial Taxable Ratio</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>COMMERCIAL_ASSESSMENT_RATIO</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr"/>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Centrally Assessed / Commercial</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Commercial AV Lag (years)</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="n">
-        <v>2</v>
+          <t>Centrally Assessed Property (market value)</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>COMM_ASSESSMENT_LAG_YEARS</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr"/>
+          <t>CENTRALLY_ASSESSED_VALUE</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>$ market — § 59-2-201</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Include Commercial in Taxed AV</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>Centrally Assessed Equipment (market value)</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>COMM_NEW_VALUE_ADD</t>
+          <t>CENTRALLY_ASSESSED_EQUIPMENT</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>$ market</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>District Costs</t>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Centrally Assessed Taxable Ratio</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>CENTRALLY_ASSESSED_RATIO</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>market value × ratio</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Annual District Administration</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="n">
-        <v>53060</v>
+          <t>Include Centrally Assessed in Taxed Value</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>ADMIN_COST</t>
+          <t>CENTRALLY_ASSESSED</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>$ per year, charged against pledged revenue</t>
+          <t>Yes/No</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>District Administration Growth Rate</t>
+          <t>Commercial Taxable Ratio</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>0.02</v>
+        <v>0.29</v>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>ADMIN_GROWTH_RATE</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t>annual inflation on the administration base</t>
-        </is>
-      </c>
+          <t>COMMERCIAL_ASSESSMENT_RATIO</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>District Administration Taxable Value Limit</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="n">
-        <v>0</v>
+          <t>Commercial AV Lag (years)</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>ADMIN_COST_AV_LIMIT</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>$ — above this taxable value the charge stops; 0 ⇒ no limit</t>
-        </is>
-      </c>
+          <t>COMM_ASSESSMENT_LAG_YEARS</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Starting O&amp;M Expense</t>
-        </is>
-      </c>
-      <c r="C100" s="10" t="n">
-        <v>0</v>
+          <t>Include Commercial in Taxed AV</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>OM_EXPENSE</t>
+          <t>COMM_NEW_VALUE_ADD</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>$ per year of district operations &amp; maintenance, netted from the revenue available to both liens</t>
+          <t>Yes/No</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>O&amp;M Expense Growth Rate</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>OM_GROWTH_RATE</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>annual inflation on the O&amp;M base</t>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>District Costs</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
+          <t>Annual District Administration</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="n">
+        <v>53060</v>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>ADMIN_COST</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>$ per year, charged against pledged revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>District Administration Growth Rate</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>ADMIN_GROWTH_RATE</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>annual inflation on the administration base</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>District Administration Taxable Value Limit</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>ADMIN_COST_AV_LIMIT</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>$ — above this taxable value the charge stops; 0 ⇒ no limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Starting O&amp;M Expense</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>OM_EXPENSE</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>$ per year of district operations &amp; maintenance, netted from the revenue available to both liens</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>O&amp;M Expense Growth Rate</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>OM_GROWTH_RATE</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>annual inflation on the O&amp;M base</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="6" t="inlineStr">
+        <is>
           <t>First Year District Costs Are Charged</t>
         </is>
       </c>
-      <c r="C102" s="7" t="n"/>
-      <c r="D102" s="8" t="inlineStr">
+      <c r="C107" s="7" t="n"/>
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>DISTRICT_COST_START_YEAR</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>blank ⇒ two years after closing</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B83:E83"/>
+  <mergeCells count="21">
     <mergeCell ref="B64:E64"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B75:E75"/>
     <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B90:E90"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B93:E93"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B96:E96"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B77:E77"/>
     <mergeCell ref="G5:K5"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B101:E101"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B82:E82"/>
     <mergeCell ref="B34:E34"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="C19 C20 C21 C22 C23 C92 C95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="C19 C20 C21 C22 C23 C97 C100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="C61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Senior,Subordinate,Proportional"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ut_pid_model_inputs - Viridian Farm.xlsx
+++ b/ut_pid_model_inputs - Viridian Farm.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:K107"/>
+  <dimension ref="B1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2298,7 +2298,7 @@
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Annual District Administration</t>
+          <t>Starting O&amp;M Expense</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
@@ -2306,19 +2306,19 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>ADMIN_COST</t>
+          <t>OM_EXPENSE</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>$ per year, charged against pledged revenue</t>
+          <t>$ per year of district operations &amp; administration, netted from the revenue available to both liens</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>District Administration Growth Rate</t>
+          <t>O&amp;M Expense Growth Rate</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
@@ -2326,19 +2326,19 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>ADMIN_GROWTH_RATE</t>
+          <t>OM_GROWTH_RATE</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>annual inflation on the administration base</t>
+          <t>annual inflation on the O&amp;M base</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>District Administration Taxable Value Limit</t>
+          <t>O&amp;M Expense Taxable Value Limit</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>ADMIN_COST_AV_LIMIT</t>
+          <t>OM_EXPENSE_AV_LIMIT</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -2358,56 +2358,16 @@
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Starting O&amp;M Expense</t>
-        </is>
-      </c>
-      <c r="C105" s="10" t="n">
-        <v>0</v>
-      </c>
+          <t>First Year District Costs Are Charged</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n"/>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>OM_EXPENSE</t>
+          <t>DISTRICT_COST_START_YEAR</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t>$ per year of district operations &amp; maintenance, netted from the revenue available to both liens</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>O&amp;M Expense Growth Rate</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D106" s="8" t="inlineStr">
-        <is>
-          <t>OM_GROWTH_RATE</t>
-        </is>
-      </c>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t>annual inflation on the O&amp;M base</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>First Year District Costs Are Charged</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="n"/>
-      <c r="D107" s="8" t="inlineStr">
-        <is>
-          <t>DISTRICT_COST_START_YEAR</t>
-        </is>
-      </c>
-      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>blank ⇒ two years after closing</t>
         </is>

--- a/ut_pid_model_inputs - Viridian Farm.xlsx
+++ b/ut_pid_model_inputs - Viridian Farm.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy.m.d"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
